--- a/Design-Files/ArmBand-Control-Board/Project Outputs for ArmBand-Control-Board/ArmBand-Control-Board.xlsx
+++ b/Design-Files/ArmBand-Control-Board/Project Outputs for ArmBand-Control-Board/ArmBand-Control-Board.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Design-Files\ArmBand-Contrrol-Board\Project Outputs for ArmBand-Control-Board\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ManarHarake-sEMGDevice\Design-Files\ArmBand-Control-Board\Project Outputs for ArmBand-Control-Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5E630DB-813B-4AAA-B68E-0B4EFC15ACF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6A31F2-8EF3-46E4-A4E8-0110AC815152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17010" yWindow="240" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22560" yWindow="2385" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="263">
   <si>
     <t>Component list</t>
   </si>
@@ -65,10 +65,13 @@
     <t>Designator</t>
   </si>
   <si>
+    <t>ANT</t>
+  </si>
+  <si>
     <t>C1, C2, C7</t>
   </si>
   <si>
-    <t>C3, C4, C6, C10, C11, C12, C13, C14, C15, C18, C19, C20, C21, C22, C24, C31, C34, C35, C36, C37, C41, C42, C47, C49</t>
+    <t>C3, C4, C6, C10, C11, C12, C13, C14, C15, C18, C19, C20, C21, C22, C23, C24, C31, C34, C35, C36, C41, C42, C47, C49</t>
   </si>
   <si>
     <t>C5</t>
@@ -77,21 +80,24 @@
     <t>C8, C25, C26, C27, C28, C39, C40, C50</t>
   </si>
   <si>
-    <t>C9, C23, C33</t>
-  </si>
-  <si>
-    <t>C16, C30, C32, C43, C45, C46, C48, C51</t>
+    <t>C9, C33</t>
+  </si>
+  <si>
+    <t>C16, C32, C43, C45, C46, C48, C51</t>
   </si>
   <si>
     <t>C17</t>
   </si>
   <si>
-    <t>C29, C44</t>
+    <t>C37</t>
   </si>
   <si>
     <t>C38</t>
   </si>
   <si>
+    <t>C44</t>
+  </si>
+  <si>
     <t>J1</t>
   </si>
   <si>
@@ -116,9 +122,6 @@
     <t>L1</t>
   </si>
   <si>
-    <t>L2</t>
-  </si>
-  <si>
     <t>L3</t>
   </si>
   <si>
@@ -149,10 +152,7 @@
     <t>R4, R5, R6, R12, R18, R19, R22, R23, R25, R27</t>
   </si>
   <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>R8, R13, R14, R15, R16, R17, R26</t>
+    <t>R7, R8, R13, R14, R15, R16, R17, R26</t>
   </si>
   <si>
     <t>R10, R11</t>
@@ -167,7 +167,7 @@
     <t>SB1, SB2, SB3</t>
   </si>
   <si>
-    <t>SW1</t>
+    <t>SW1, SW2</t>
   </si>
   <si>
     <t>U1</t>
@@ -227,24 +227,27 @@
     <t>CAP CER 2.2UF 25V X5R 0402</t>
   </si>
   <si>
+    <t>0402 100 pF 50 V ±5 % Tolerance C0G SMT Multilayer Ceramic Capacitor</t>
+  </si>
+  <si>
+    <t>CAP CER 0.8PF 50V C0G/NP0 0402</t>
+  </si>
+  <si>
     <t>CAP CER 1000PF 25V X7R 0402</t>
   </si>
   <si>
-    <t>CAP CER 0.8PF 50V C0G/NP0 0402</t>
-  </si>
-  <si>
     <t>CONN U.FL RCPT STR 50 OHM SMD</t>
   </si>
   <si>
+    <t>Clamshell 22 Double-sided contacts/up and down connection Surface Mount 0.5mm SMD,P=0.5mm FFC/FPC Connectors ROHS</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 2POS 1.5MM</t>
+  </si>
+  <si>
     <t>CONN RCP USB3.1 TYPEC 24P SMD RA</t>
   </si>
   <si>
-    <t>CONN HEADER VERT 2POS 1.5MM</t>
-  </si>
-  <si>
-    <t>Clamshell 22 Double-sided contacts/up and down connection Surface Mount 0.5mm SMD,P=0.5mm FFC/FPC Connectors ROHS</t>
-  </si>
-  <si>
     <t>CONN HEADER VERT 8POS 2.54MM</t>
   </si>
   <si>
@@ -257,9 +260,6 @@
     <t>FIXED IND 2.2UH 1.5A 160MOHM SMD</t>
   </si>
   <si>
-    <t>FIXED IND 10UH 360MA 1.32OHM SMD</t>
-  </si>
-  <si>
     <t>500mA 10uH ±20% 320mΩ 0805 Inductors (SMD) ROHS</t>
   </si>
   <si>
@@ -290,9 +290,6 @@
     <t>RES SMD 10K OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>62.5mW Thick Film Resistors 50V ±5% ±200ppm/℃ 1Ω -55℃~+155℃ 0402 Chip Resistor - Surface Mount ROHS</t>
-  </si>
-  <si>
     <t>RES SMD 100K OHM 1% 1/5W 0402</t>
   </si>
   <si>
@@ -347,6 +344,9 @@
     <t>Footprint</t>
   </si>
   <si>
+    <t>ANT#</t>
+  </si>
+  <si>
     <t>Cap0805</t>
   </si>
   <si>
@@ -359,15 +359,15 @@
     <t>U.FL-R-SMT-1(80)</t>
   </si>
   <si>
+    <t>F0504-H-22-20T-R</t>
+  </si>
+  <si>
+    <t>B2B-ZR(LF)(SN)</t>
+  </si>
+  <si>
     <t>2305018-2</t>
   </si>
   <si>
-    <t>B2B-ZR(LF)(SN)</t>
-  </si>
-  <si>
-    <t>F0504-H-22-20T-R</t>
-  </si>
-  <si>
     <t>HDR1X8</t>
   </si>
   <si>
@@ -380,9 +380,6 @@
     <t>MAKK2016T2R2M</t>
   </si>
   <si>
-    <t>NLCV25T-100K-EFRD</t>
-  </si>
-  <si>
     <t>Ind0805</t>
   </si>
   <si>
@@ -470,12 +467,15 @@
     <t>GRM155R61E225KE11D</t>
   </si>
   <si>
+    <t>GCM1555C1H101JA16D</t>
+  </si>
+  <si>
+    <t>GJM1555C1HR80WB01D</t>
+  </si>
+  <si>
     <t>CC0402KRX7R8BB102</t>
   </si>
   <si>
-    <t>GJM1555C1HR80WB01D</t>
-  </si>
-  <si>
     <t>MGFL2012F100MT-LF</t>
   </si>
   <si>
@@ -497,9 +497,6 @@
     <t>RC0402FR-0710KL</t>
   </si>
   <si>
-    <t>FRC0402J1R0 TS</t>
-  </si>
-  <si>
     <t>ERJ-PA2F1003X</t>
   </si>
   <si>
@@ -557,21 +554,18 @@
     <t>Hirose</t>
   </si>
   <si>
+    <t>XFCN</t>
+  </si>
+  <si>
+    <t>JST</t>
+  </si>
+  <si>
     <t>TE Connectivity AMP</t>
   </si>
   <si>
-    <t>JST</t>
-  </si>
-  <si>
-    <t>XFCN</t>
-  </si>
-  <si>
     <t>Wurth Electronics</t>
   </si>
   <si>
-    <t>TDK</t>
-  </si>
-  <si>
     <t>microgate</t>
   </si>
   <si>
@@ -587,9 +581,6 @@
     <t>UNI-Royal Elec</t>
   </si>
   <si>
-    <t>FOJAN</t>
-  </si>
-  <si>
     <t>Panasonic</t>
   </si>
   <si>
@@ -632,6 +623,9 @@
     <t>Comment</t>
   </si>
   <si>
+    <t>Antenna</t>
+  </si>
+  <si>
     <t>22uF</t>
   </si>
   <si>
@@ -653,12 +647,15 @@
     <t>2.2uF</t>
   </si>
   <si>
+    <t>100pF</t>
+  </si>
+  <si>
+    <t>0.8pF</t>
+  </si>
+  <si>
     <t>1nF</t>
   </si>
   <si>
-    <t>0.8pF</t>
-  </si>
-  <si>
     <t>2.2uH</t>
   </si>
   <si>
@@ -683,9 +680,6 @@
     <t>10K</t>
   </si>
   <si>
-    <t>1R</t>
-  </si>
-  <si>
     <t>100K</t>
   </si>
   <si>
@@ -725,24 +719,27 @@
     <t>http://www.yageo.com/documents/recent/UPY-GPHC_X5R_4V-to-50V_12.pdf?src-supplier=Avnet+Europe</t>
   </si>
   <si>
+    <t>https://datasheet.ciiva.com/26889/getdatasheetpartid-748988-26889122.pdf?src-supplier=Verical</t>
+  </si>
+  <si>
+    <t>https://datasheet.ciiva.com/170/product-170100.pdf?src-supplier=Digi-Key</t>
+  </si>
+  <si>
     <t>https://datasheet.ciiva.com/26862/getdatasheetpartid-639817-26862638.pdf?src-supplier=Verical</t>
   </si>
   <si>
-    <t>https://datasheet.ciiva.com/170/product-170100.pdf?src-supplier=Digi-Key</t>
-  </si>
-  <si>
     <t>https://www.hirose.com/product/en/download_file/key_name/U.FL-R-SMT-1%2880%29/category/Specification%20Sheet/doc_file_id/37638/?file_category_id=9&amp;item_id=03310472280&amp;is_series=&amp;src-supplier=Digi-Key</t>
   </si>
   <si>
+    <t>https://lcsc.com/product-detail/FFC-FPC-Connectors_XFCN-F0504-H-22-20T-R_C557729.html</t>
+  </si>
+  <si>
+    <t>https://datasheet.ciiva.com/11752/0900766b8082f580-11752167.pdf?src-supplier=RSComponents</t>
+  </si>
+  <si>
     <t>http://www.farnell.com/datasheets/2611889.pdf?src-supplier=Farnell</t>
   </si>
   <si>
-    <t>https://datasheet.ciiva.com/11752/0900766b8082f580-11752167.pdf?src-supplier=RSComponents</t>
-  </si>
-  <si>
-    <t>https://lcsc.com/product-detail/FFC-FPC-Connectors_XFCN-F0504-H-22-20T-R_C557729.html</t>
-  </si>
-  <si>
     <t>http://www.farnell.com/cad/1737268.pdf?src-supplier=Element14</t>
   </si>
   <si>
@@ -752,9 +749,6 @@
     <t>https://datasheet.ciiva.com/30014/makk2016t2r2m-ss-30014449.pdf?src-supplier=Avnet</t>
   </si>
   <si>
-    <t>https://product.tdk.com/info/en/catalog/datasheets/inductor_automotive_decoupling_nlcv25-efrd_en.pdf?ref_disty=digikey&amp;src-supplier=Digi-Key</t>
-  </si>
-  <si>
     <t>https://lcsc.com/product-detail/Inductors-SMD_Sunltech-Tech-SCW1608C15NJST_C231879.html</t>
   </si>
   <si>
@@ -780,9 +774,6 @@
   </si>
   <si>
     <t>http://www.farnell.com/datasheets/2167052.pdf?src-supplier=Element14</t>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/Chip-Resistor-Surface-Mount_FOJAN-FRC0402J1R0-TS_C2906901.html</t>
   </si>
   <si>
     <t>http://www.farnell.com/datasheets/2051174.pdf?src-supplier=Element14</t>
@@ -1386,6 +1377,18 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1394,18 +1397,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1771,11 +1762,11 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
     </row>
     <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1784,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="10"/>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="51" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="11"/>
@@ -1803,7 +1794,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="12"/>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="12"/>
@@ -1813,7 +1804,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="52"/>
+      <c r="M3" s="56"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1822,7 +1813,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="12"/>
-      <c r="E4" s="56" t="s">
+      <c r="E4" s="53" t="s">
         <v>8</v>
       </c>
       <c r="F4" s="13"/>
@@ -1832,7 +1823,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="53"/>
+      <c r="M4" s="57"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1841,7 +1832,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="12"/>
-      <c r="E5" s="57" t="s">
+      <c r="E5" s="54" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="14"/>
@@ -1851,7 +1842,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="53"/>
+      <c r="M5" s="57"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1866,7 +1857,7 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="53"/>
+      <c r="M6" s="57"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1881,7 +1872,7 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="53"/>
+      <c r="M7" s="57"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1896,7 +1887,7 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="53"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1910,34 +1901,34 @@
         <v>57</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G9" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="H9" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="H9" s="29" t="s">
-        <v>169</v>
-      </c>
       <c r="I9" s="30" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K9" s="29" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="32">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -1946,32 +1937,24 @@
       <c r="C10" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="40" t="s">
-        <v>58</v>
-      </c>
+      <c r="D10" s="40"/>
       <c r="E10" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="F10" s="40" t="s">
-        <v>139</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="F10" s="40"/>
       <c r="G10" s="39"/>
-      <c r="H10" s="39" t="s">
-        <v>170</v>
-      </c>
+      <c r="H10" s="39"/>
       <c r="I10" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="J10" s="39" t="s">
-        <v>226</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="J10" s="39"/>
       <c r="K10" s="39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" s="39"/>
       <c r="M10" s="45"/>
     </row>
-    <row r="11" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="32">
         <f t="shared" ref="B11:B56" si="0">ROW(B11) - ROW($B$9)</f>
@@ -1981,31 +1964,31 @@
         <v>12</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G11" s="41"/>
       <c r="H11" s="41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I11" s="42" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="J11" s="41" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="K11" s="41">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L11" s="41"/>
       <c r="M11" s="46"/>
     </row>
-    <row r="12" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="32">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -2015,26 +1998,26 @@
         <v>13</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G12" s="39"/>
       <c r="H12" s="39" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K12" s="39">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="L12" s="39"/>
       <c r="M12" s="45"/>
@@ -2049,26 +2032,26 @@
         <v>14</v>
       </c>
       <c r="D13" s="42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G13" s="41"/>
       <c r="H13" s="41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I13" s="42" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="J13" s="41" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="K13" s="41">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L13" s="41"/>
       <c r="M13" s="46"/>
@@ -2083,29 +2066,31 @@
         <v>15</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E14" s="39" t="s">
         <v>106</v>
       </c>
       <c r="F14" s="40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G14" s="39"/>
       <c r="H14" s="39" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I14" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="J14" s="39"/>
+        <v>201</v>
+      </c>
+      <c r="J14" s="39" t="s">
+        <v>227</v>
+      </c>
       <c r="K14" s="39">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L14" s="39"/>
       <c r="M14" s="45"/>
     </row>
-    <row r="15" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="32">
         <f t="shared" si="0"/>
@@ -2115,31 +2100,29 @@
         <v>16</v>
       </c>
       <c r="D15" s="42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" s="41" t="s">
         <v>106</v>
       </c>
       <c r="F15" s="42" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G15" s="41"/>
       <c r="H15" s="41" t="s">
         <v>172</v>
       </c>
       <c r="I15" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="J15" s="41" t="s">
-        <v>230</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="J15" s="41"/>
       <c r="K15" s="41">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L15" s="41"/>
       <c r="M15" s="46"/>
     </row>
-    <row r="16" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="32">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -2149,29 +2132,31 @@
         <v>17</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E16" s="39" t="s">
         <v>106</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G16" s="39"/>
       <c r="H16" s="39" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I16" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="J16" s="39"/>
+        <v>203</v>
+      </c>
+      <c r="J16" s="39" t="s">
+        <v>228</v>
+      </c>
       <c r="K16" s="39">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L16" s="39"/>
       <c r="M16" s="45"/>
     </row>
-    <row r="17" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="32">
         <f t="shared" si="0"/>
@@ -2181,31 +2166,29 @@
         <v>18</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" s="41" t="s">
         <v>106</v>
       </c>
       <c r="F17" s="42" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G17" s="41"/>
       <c r="H17" s="41" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I17" s="42" t="s">
-        <v>207</v>
-      </c>
-      <c r="J17" s="41" t="s">
-        <v>231</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="J17" s="41"/>
       <c r="K17" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="41"/>
       <c r="M17" s="46"/>
     </row>
-    <row r="18" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="32">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -2215,23 +2198,23 @@
         <v>19</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" s="39" t="s">
         <v>106</v>
       </c>
       <c r="F18" s="40" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G18" s="39"/>
       <c r="H18" s="39" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I18" s="40" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="J18" s="39" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="K18" s="39">
         <v>1</v>
@@ -2239,7 +2222,7 @@
       <c r="L18" s="39"/>
       <c r="M18" s="45"/>
     </row>
-    <row r="19" spans="1:13" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="32">
         <f t="shared" si="0"/>
@@ -2249,23 +2232,23 @@
         <v>20</v>
       </c>
       <c r="D19" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F19" s="42" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="G19" s="41"/>
       <c r="H19" s="41" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="I19" s="42" t="s">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c r="J19" s="41" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="K19" s="41">
         <v>1</v>
@@ -2273,7 +2256,7 @@
       <c r="L19" s="41"/>
       <c r="M19" s="46"/>
     </row>
-    <row r="20" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="32">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -2283,23 +2266,23 @@
         <v>21</v>
       </c>
       <c r="D20" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F20" s="40" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="G20" s="39"/>
       <c r="H20" s="39" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I20" s="40" t="s">
-        <v>109</v>
+        <v>207</v>
       </c>
       <c r="J20" s="39" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="K20" s="39">
         <v>1</v>
@@ -2307,7 +2290,7 @@
       <c r="L20" s="39"/>
       <c r="M20" s="45"/>
     </row>
-    <row r="21" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="32">
         <f t="shared" si="0"/>
@@ -2317,23 +2300,23 @@
         <v>22</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G21" s="41"/>
       <c r="H21" s="41" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J21" s="41" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="K21" s="41">
         <v>1</v>
@@ -2351,23 +2334,23 @@
         <v>23</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F22" s="40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G22" s="39"/>
       <c r="H22" s="39" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I22" s="40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J22" s="39" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K22" s="39">
         <v>1</v>
@@ -2375,7 +2358,7 @@
       <c r="L22" s="39"/>
       <c r="M22" s="45"/>
     </row>
-    <row r="23" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="32">
         <f t="shared" si="0"/>
@@ -2385,23 +2368,23 @@
         <v>24</v>
       </c>
       <c r="D23" s="42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23" s="42">
-        <v>61300811121</v>
+        <v>110</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>110</v>
       </c>
       <c r="G23" s="41"/>
       <c r="H23" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="I23" s="42">
-        <v>61300811121</v>
+        <v>175</v>
+      </c>
+      <c r="I23" s="42" t="s">
+        <v>110</v>
       </c>
       <c r="J23" s="41" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K23" s="41">
         <v>1</v>
@@ -2409,7 +2392,7 @@
       <c r="L23" s="41"/>
       <c r="M23" s="46"/>
     </row>
-    <row r="24" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="32">
         <f>ROW(B24) - ROW($B$9)</f>
@@ -2419,23 +2402,23 @@
         <v>25</v>
       </c>
       <c r="D24" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F24" s="40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G24" s="39"/>
       <c r="H24" s="39" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I24" s="40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J24" s="39" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K24" s="39">
         <v>1</v>
@@ -2453,23 +2436,23 @@
         <v>26</v>
       </c>
       <c r="D25" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F25" s="42">
-        <v>61300411121</v>
+        <v>61300811121</v>
       </c>
       <c r="G25" s="41"/>
       <c r="H25" s="41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I25" s="42">
-        <v>61300411121</v>
+        <v>61300811121</v>
       </c>
       <c r="J25" s="41" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K25" s="41">
         <v>1</v>
@@ -2477,7 +2460,7 @@
       <c r="L25" s="41"/>
       <c r="M25" s="46"/>
     </row>
-    <row r="26" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="32">
         <f>ROW(B26) - ROW($B$9)</f>
@@ -2487,23 +2470,23 @@
         <v>27</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F26" s="40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G26" s="39"/>
       <c r="H26" s="39" t="s">
         <v>173</v>
       </c>
       <c r="I26" s="40" t="s">
-        <v>209</v>
+        <v>113</v>
       </c>
       <c r="J26" s="39" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="K26" s="39">
         <v>1</v>
@@ -2511,7 +2494,7 @@
       <c r="L26" s="39"/>
       <c r="M26" s="45"/>
     </row>
-    <row r="27" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="32">
         <f t="shared" si="0"/>
@@ -2521,23 +2504,23 @@
         <v>28</v>
       </c>
       <c r="D27" s="42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>116</v>
+        <v>114</v>
+      </c>
+      <c r="F27" s="42">
+        <v>61300411121</v>
       </c>
       <c r="G27" s="41"/>
       <c r="H27" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="I27" s="42" t="s">
-        <v>210</v>
+        <v>177</v>
+      </c>
+      <c r="I27" s="42">
+        <v>61300411121</v>
       </c>
       <c r="J27" s="41" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K27" s="41">
         <v>1</v>
@@ -2555,29 +2538,31 @@
         <v>29</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F28" s="40" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="G28" s="39"/>
       <c r="H28" s="39" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="I28" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="J28" s="39"/>
+        <v>208</v>
+      </c>
+      <c r="J28" s="39" t="s">
+        <v>238</v>
+      </c>
       <c r="K28" s="39">
         <v>1</v>
       </c>
       <c r="L28" s="39"/>
       <c r="M28" s="45"/>
     </row>
-    <row r="29" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="32">
         <f t="shared" si="0"/>
@@ -2587,31 +2572,29 @@
         <v>30</v>
       </c>
       <c r="D29" s="42" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E29" s="41" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="G29" s="41"/>
       <c r="H29" s="41" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>211</v>
-      </c>
-      <c r="J29" s="41" t="s">
-        <v>241</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="J29" s="41"/>
       <c r="K29" s="41">
         <v>1</v>
       </c>
       <c r="L29" s="41"/>
       <c r="M29" s="46"/>
     </row>
-    <row r="30" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="32">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -2621,23 +2604,23 @@
         <v>31</v>
       </c>
       <c r="D30" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E30" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F30" s="40" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="G30" s="39"/>
       <c r="H30" s="39" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="I30" s="40" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J30" s="39" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="K30" s="39">
         <v>1</v>
@@ -2655,23 +2638,23 @@
         <v>32</v>
       </c>
       <c r="D31" s="42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E31" s="41" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G31" s="41"/>
       <c r="H31" s="41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I31" s="42" t="s">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="J31" s="41" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="K31" s="41">
         <v>1</v>
@@ -2679,7 +2662,7 @@
       <c r="L31" s="41"/>
       <c r="M31" s="46"/>
     </row>
-    <row r="32" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="32">
         <f>ROW(B32) - ROW($B$9)</f>
@@ -2689,23 +2672,23 @@
         <v>33</v>
       </c>
       <c r="D32" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E32" s="39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F32" s="40" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G32" s="39"/>
       <c r="H32" s="39" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I32" s="40" t="s">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="J32" s="39" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K32" s="39">
         <v>1</v>
@@ -2713,7 +2696,7 @@
       <c r="L32" s="39"/>
       <c r="M32" s="45"/>
     </row>
-    <row r="33" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="32">
         <f t="shared" si="0"/>
@@ -2723,26 +2706,26 @@
         <v>34</v>
       </c>
       <c r="D33" s="42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E33" s="41" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="G33" s="41"/>
       <c r="H33" s="41" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I33" s="42" t="s">
-        <v>151</v>
+        <v>212</v>
       </c>
       <c r="J33" s="41" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="K33" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="41"/>
       <c r="M33" s="46"/>
@@ -2757,31 +2740,31 @@
         <v>35</v>
       </c>
       <c r="D34" s="40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E34" s="39" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G34" s="39"/>
       <c r="H34" s="39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I34" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J34" s="39" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="K34" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="39"/>
       <c r="M34" s="45"/>
     </row>
-    <row r="35" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="32">
         <f t="shared" si="0"/>
@@ -2791,21 +2774,23 @@
         <v>36</v>
       </c>
       <c r="D35" s="42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E35" s="41" t="s">
-        <v>122</v>
-      </c>
-      <c r="F35" s="42"/>
+        <v>120</v>
+      </c>
+      <c r="F35" s="42" t="s">
+        <v>152</v>
+      </c>
       <c r="G35" s="41"/>
       <c r="H35" s="41" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I35" s="42" t="s">
-        <v>214</v>
+        <v>152</v>
       </c>
       <c r="J35" s="41" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="K35" s="41">
         <v>1</v>
@@ -2813,7 +2798,7 @@
       <c r="L35" s="41"/>
       <c r="M35" s="46"/>
     </row>
-    <row r="36" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="32">
         <f>ROW(B36) - ROW($B$9)</f>
@@ -2823,26 +2808,24 @@
         <v>37</v>
       </c>
       <c r="D36" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E36" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="F36" s="40" t="s">
-        <v>153</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="F36" s="40"/>
       <c r="G36" s="39"/>
       <c r="H36" s="39" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="I36" s="40" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J36" s="39" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="K36" s="39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L36" s="39"/>
       <c r="M36" s="45"/>
@@ -2857,31 +2840,31 @@
         <v>38</v>
       </c>
       <c r="D37" s="42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E37" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G37" s="41"/>
       <c r="H37" s="41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I37" s="42" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J37" s="41" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K37" s="41">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L37" s="41"/>
       <c r="M37" s="46"/>
     </row>
-    <row r="38" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="32">
         <f>ROW(B38) - ROW($B$9)</f>
@@ -2891,26 +2874,26 @@
         <v>39</v>
       </c>
       <c r="D38" s="40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E38" s="39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F38" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G38" s="39"/>
       <c r="H38" s="39" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="I38" s="40" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="K38" s="39">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L38" s="39"/>
       <c r="M38" s="45"/>
@@ -2925,26 +2908,26 @@
         <v>40</v>
       </c>
       <c r="D39" s="42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G39" s="41"/>
       <c r="H39" s="41" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I39" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J39" s="41" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="K39" s="41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L39" s="41"/>
       <c r="M39" s="46"/>
@@ -2959,23 +2942,23 @@
         <v>41</v>
       </c>
       <c r="D40" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F40" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G40" s="39"/>
       <c r="H40" s="39" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I40" s="40" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K40" s="39">
         <v>2</v>
@@ -2993,23 +2976,23 @@
         <v>42</v>
       </c>
       <c r="D41" s="42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F41" s="42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G41" s="41"/>
       <c r="H41" s="41" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="I41" s="42" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J41" s="41" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="K41" s="41">
         <v>2</v>
@@ -3027,20 +3010,20 @@
         <v>43</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F42" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G42" s="39"/>
       <c r="H42" s="39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I42" s="40" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J42" s="39"/>
       <c r="K42" s="39">
@@ -3059,16 +3042,16 @@
         <v>44</v>
       </c>
       <c r="D43" s="42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E43" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="41"/>
       <c r="H43" s="41"/>
       <c r="I43" s="42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J43" s="41"/>
       <c r="K43" s="41">
@@ -3087,26 +3070,26 @@
         <v>45</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F44" s="40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G44" s="39"/>
       <c r="H44" s="39" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I44" s="40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="K44" s="39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" s="39"/>
       <c r="M44" s="45"/>
@@ -3121,20 +3104,20 @@
         <v>46</v>
       </c>
       <c r="D45" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E45" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F45" s="42" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G45" s="41"/>
       <c r="H45" s="41" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="I45" s="42" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J45" s="41"/>
       <c r="K45" s="41">
@@ -3153,23 +3136,23 @@
         <v>47</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F46" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G46" s="39"/>
       <c r="H46" s="39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I46" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J46" s="39" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="K46" s="39">
         <v>1</v>
@@ -3187,23 +3170,23 @@
         <v>48</v>
       </c>
       <c r="D47" s="42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E47" s="41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F47" s="42" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G47" s="41"/>
       <c r="H47" s="41" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I47" s="42" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J47" s="41" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="K47" s="41">
         <v>1</v>
@@ -3221,23 +3204,23 @@
         <v>49</v>
       </c>
       <c r="D48" s="40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E48" s="39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F48" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G48" s="39"/>
       <c r="H48" s="39" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="I48" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J48" s="39" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K48" s="39">
         <v>1</v>
@@ -3255,23 +3238,23 @@
         <v>50</v>
       </c>
       <c r="D49" s="42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E49" s="41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F49" s="42" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G49" s="41"/>
       <c r="H49" s="41" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I49" s="42" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J49" s="41" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="K49" s="41">
         <v>1</v>
@@ -3289,20 +3272,20 @@
         <v>51</v>
       </c>
       <c r="D50" s="40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F50" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G50" s="39"/>
       <c r="H50" s="39" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I50" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J50" s="39"/>
       <c r="K50" s="39">
@@ -3321,23 +3304,23 @@
         <v>52</v>
       </c>
       <c r="D51" s="42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E51" s="41" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F51" s="42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G51" s="41"/>
       <c r="H51" s="41" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I51" s="42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J51" s="41" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="K51" s="41">
         <v>1</v>
@@ -3355,23 +3338,23 @@
         <v>53</v>
       </c>
       <c r="D52" s="40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E52" s="39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F52" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G52" s="39"/>
       <c r="H52" s="39" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I52" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="K52" s="39">
         <v>1</v>
@@ -3389,23 +3372,23 @@
         <v>54</v>
       </c>
       <c r="D53" s="42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E53" s="41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F53" s="42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G53" s="41"/>
       <c r="H53" s="41" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I53" s="42" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J53" s="41" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="K53" s="41">
         <v>2</v>
@@ -3423,23 +3406,23 @@
         <v>55</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E54" s="39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F54" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G54" s="39"/>
       <c r="H54" s="39" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I54" s="40" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J54" s="39" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="K54" s="39">
         <v>1</v>
@@ -3457,20 +3440,20 @@
         <v>56</v>
       </c>
       <c r="D55" s="42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E55" s="41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F55" s="42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G55" s="41"/>
       <c r="H55" s="41" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I55" s="42" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J55" s="41"/>
       <c r="K55" s="41">
